--- a/tame_output/ON/bt/strategyON_20240319.xlsx
+++ b/tame_output/ON/bt/strategyON_20240319.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-59.1%</t>
+          <t>-60.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>102.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>112.3%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-443.5%</t>
+          <t>-479.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,27 +992,27 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-37.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-52.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>490.0%</t>
+          <t>-105.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-337.8%</t>
+          <t>-341.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-177.8%</t>
+          <t>-192.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-130.3%</t>
+          <t>-131.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-36.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-67.6%</t>
+          <t>-34.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>102.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>103.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-16.1%</t>
         </is>
       </c>
     </row>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3421514795106159</v>
+        <v>-0.01774990557364237</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.262984887028284</v>
+        <v>3.119024332994581</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2603795790828642</v>
+        <v>-0.09952180600139404</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.220358852812422</v>
+        <v>3.076398298778719</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1931704712109866</v>
+        <v>-0.1667309138732717</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.198240526497373</v>
+        <v>3.05427997246367</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1971619240061768</v>
+        <v>-0.1627394610780815</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.19766190373469</v>
+        <v>3.053701349700986</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>0.04546487696224172</v>
+        <v>-0.3144365081220166</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.134909976422179</v>
+        <v>2.990949422388475</v>
       </c>
       <c r="F1847" t="n">
         <v>1.69689596888862</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.1761570565958758</v>
+        <v>-0.5360584416801341</v>
       </c>
       <c r="E1848" t="n">
-        <v>3.046127419597854</v>
+        <v>2.90216686556415</v>
       </c>
       <c r="F1848" t="n">
         <v>1.659369835201251</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.384161114948953</v>
+        <v>-0.7440625000332113</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.967817940810548</v>
+        <v>2.823857386776845</v>
       </c>
       <c r="F1849" t="n">
         <v>1.659369835201251</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.6545610776578383</v>
+        <v>-1.014462462742097</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.854739412064982</v>
+        <v>2.710778858031278</v>
       </c>
       <c r="F1850" t="n">
         <v>1.388969872492366</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-0.6611960001547685</v>
+        <v>-1.021097385239027</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.845169742372659</v>
+        <v>2.701209188338956</v>
       </c>
       <c r="F1851" t="n">
         <v>1.382334949995436</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-0.9892132218822477</v>
+        <v>-1.349114606966506</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.734301143420435</v>
+        <v>2.590340589386732</v>
       </c>
       <c r="F1852" t="n">
         <v>1.054317728267957</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-0.9858764753732761</v>
+        <v>-1.345777860457534</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.743734592432593</v>
+        <v>2.599774038398889</v>
       </c>
       <c r="F1853" t="n">
         <v>1.057009760686988</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.352587527039822</v>
+        <v>-1.71248891212408</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.598156563809707</v>
+        <v>2.454196009776003</v>
       </c>
       <c r="F1854" t="n">
         <v>0.6902987090204425</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-1.353018226088417</v>
+        <v>-1.712919611172675</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.596526823003132</v>
+        <v>2.452566268969429</v>
       </c>
       <c r="F1855" t="n">
         <v>0.6902987090204425</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-1.69670099931508</v>
+        <v>-2.056602384399338</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.460822837167083</v>
+        <v>2.316862283133379</v>
       </c>
       <c r="F1856" t="n">
         <v>0.5823926569932243</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-2.054351349553428</v>
+        <v>-2.414252734637686</v>
       </c>
       <c r="E1857" t="n">
-        <v>2.313868755728001</v>
+        <v>2.169908201694298</v>
       </c>
       <c r="F1857" t="n">
         <v>0.2247423067548762</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-2.061012289775575</v>
+        <v>-2.420913674859834</v>
       </c>
       <c r="E1858" t="n">
-        <v>2.312977306339402</v>
+        <v>2.169016752305699</v>
       </c>
       <c r="F1858" t="n">
         <v>0.2247423067548762</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-2.492818082925363</v>
+        <v>-2.852719468009622</v>
       </c>
       <c r="E1859" t="n">
-        <v>2.126587876546891</v>
+        <v>1.982627322513188</v>
       </c>
       <c r="F1859" t="n">
         <v>0.08832481031360917</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-2.819250611793107</v>
+        <v>-3.179151996877365</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.984299640001884</v>
+        <v>1.840339085968181</v>
       </c>
       <c r="F1860" t="n">
         <v>0.005856559806460993</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-2.82081476290341</v>
+        <v>-3.180716147987668</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.982254571213728</v>
+        <v>1.838294017180025</v>
       </c>
       <c r="F1861" t="n">
         <v>0.005856559806460993</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-3.184441007803723</v>
+        <v>-3.544342392887981</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.843291633487845</v>
+        <v>1.699331079454141</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.09236507706066482</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-3.182013943275004</v>
+        <v>-3.541915328359263</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.843516974305163</v>
+        <v>1.69955642027146</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.09269785886781645</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-3.590602720455683</v>
+        <v>-3.950504105539941</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.678843007447651</v>
+        <v>1.534882453413948</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.5012866360484949</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.003585204596776</v>
+        <v>-4.363486589681035</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.508835446262674</v>
+        <v>1.364874892228971</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.5012866360484949</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-4.419977078883774</v>
+        <v>-4.779878463968032</v>
       </c>
       <c r="E1866" t="n">
-        <v>1.340272747156753</v>
+        <v>1.196312193123049</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.5012866360484949</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-4.796654089413618</v>
+        <v>-5.156555474497877</v>
       </c>
       <c r="E1867" t="n">
-        <v>1.199860633613494</v>
+        <v>1.055900079579791</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.5012866360484949</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-4.810368953738729</v>
+        <v>-5.170270338822988</v>
       </c>
       <c r="E1868" t="n">
-        <v>1.190474253029145</v>
+        <v>1.046513698995441</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.5012866360484949</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-5.123193752983709</v>
+        <v>-5.483095138067967</v>
       </c>
       <c r="E1869" t="n">
-        <v>1.063749253386153</v>
+        <v>0.9197886993524502</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.5012866360484949</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-5.128006791449046</v>
+        <v>-5.487908176533304</v>
       </c>
       <c r="E1870" t="n">
-        <v>1.065603013929227</v>
+        <v>0.9216424598955237</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.5028332707512807</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-5.561355899559282</v>
+        <v>-5.921257284643541</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.8882370661507295</v>
+        <v>0.7442765121170258</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.5028332707512807</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-5.944357288301913</v>
+        <v>-6.304258673386172</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.7349344093320931</v>
+        <v>0.5909738552983894</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.5028332707512807</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-6.31934261447319</v>
+        <v>-6.679243999557449</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.5875117948350121</v>
+        <v>0.4435512408013085</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8778185969225581</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-6.678872936977192</v>
+        <v>-7.03877432206145</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.4490499691314618</v>
+        <v>0.3050894150977581</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8778185969225581</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.005272965642205</v>
+        <v>-7.365174350726464</v>
       </c>
       <c r="E1875" t="n">
-        <v>0.3264059776226338</v>
+        <v>0.1824454235889306</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.204218625587571</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-6.998796818848645</v>
+        <v>-7.358698203932904</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.3320381869618267</v>
+        <v>0.1880776329281231</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.197742478794011</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-6.995105893892234</v>
+        <v>-7.355007278976492</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.3335145569443911</v>
+        <v>0.1895540029106879</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.197742478794011</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-6.987890541020418</v>
+        <v>-7.347791926104676</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.3419138952117597</v>
+        <v>0.1979533411780565</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.12796424350363</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-6.936862694938592</v>
+        <v>-7.29676408002285</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.3668075881289266</v>
+        <v>0.2228470340952229</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.052754905196529</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-6.863392863271144</v>
+        <v>-7.223294248355402</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.4115672222893267</v>
+        <v>0.2676066682556235</v>
       </c>
       <c r="F1880" t="n">
         <v>-0.9792850735290801</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-6.783020507807214</v>
+        <v>-7.142921892891472</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.4582713852224156</v>
+        <v>0.3143108311887124</v>
       </c>
       <c r="F1881" t="n">
         <v>-0.8989127180651505</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880266</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-6.971293310173058</v>
+        <v>-7.331194695257317</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.3757430993744819</v>
+        <v>0.2317825453407782</v>
       </c>
       <c r="F1882" t="n">
         <v>-0.8989127180651505</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234391</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-6.991457951722605</v>
+        <v>-7.351359336806864</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.3610050519806869</v>
+        <v>0.2170444979469832</v>
       </c>
       <c r="F1883" t="n">
         <v>-0.9190773596146978</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860581</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-7.22128239888643</v>
+        <v>-7.581183783970689</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.270191062953713</v>
+        <v>0.1262305089200098</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.081724896684858</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767394</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-7.158213166580091</v>
+        <v>-7.518114551664349</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.2981124845053635</v>
+        <v>0.1541519304716599</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.110238459367093</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792538</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-7.106197652611279</v>
+        <v>-7.466099037695537</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.322909025779289</v>
+        <v>0.1789484717455858</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.110238459367093</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628916</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-6.930627983690375</v>
+        <v>-7.290529368774633</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.391661666448909</v>
+        <v>0.2477011124152058</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.110238459367093</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410712</v>
+        <v>3.691568158410713</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-6.733358577962377</v>
+        <v>-7.093259963046635</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.4856228389049808</v>
+        <v>0.3416622848712771</v>
       </c>
       <c r="F1888" t="n">
         <v>-0.9129690536390945</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-6.534206470725278</v>
+        <v>-6.894107855809536</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.5522325481531372</v>
+        <v>0.4082719941194339</v>
       </c>
       <c r="F1889" t="n">
         <v>-0.7476465276892812</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085275</v>
+        <v>3.685157806085276</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-6.308361318005867</v>
+        <v>-6.668262703090125</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.6521496822771105</v>
+        <v>0.5081891282434068</v>
       </c>
       <c r="F1890" t="n">
         <v>-0.7057198521021175</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-6.022086505683172</v>
+        <v>-6.381987890767431</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.7677987517622467</v>
+        <v>0.6238381977285434</v>
       </c>
       <c r="F1891" t="n">
         <v>-0.7057198521021175</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-5.795290678609839</v>
+        <v>-6.155192063694098</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.8611508567536879</v>
+        <v>0.7171903027199846</v>
       </c>
       <c r="F1892" t="n">
         <v>-0.637605907480573</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-5.51138194768109</v>
+        <v>-5.871283332765349</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.980448053363824</v>
+        <v>0.8364874993301208</v>
       </c>
       <c r="F1893" t="n">
         <v>-0.637605907480573</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-5.264394697488138</v>
+        <v>-5.624296082572396</v>
       </c>
       <c r="E1894" t="n">
-        <v>1.06950569104714</v>
+        <v>0.9255451370134362</v>
       </c>
       <c r="F1894" t="n">
         <v>-0.3906186572876209</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-5.000557830284069</v>
+        <v>-5.360459215368327</v>
       </c>
       <c r="E1895" t="n">
-        <v>1.16515695661586</v>
+        <v>1.021196402582156</v>
       </c>
       <c r="F1895" t="n">
         <v>-0.3906186572876209</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-4.733316029415672</v>
+        <v>-5.09321741449993</v>
       </c>
       <c r="E1896" t="n">
-        <v>1.270219116463845</v>
+        <v>1.126258562430142</v>
       </c>
       <c r="F1896" t="n">
         <v>-0.3906186572876209</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-4.457506866015188</v>
+        <v>-4.817408251099446</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.380242466850577</v>
+        <v>1.236281912816874</v>
       </c>
       <c r="F1897" t="n">
         <v>-0.3015993490088874</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-4.188439278248208</v>
+        <v>-4.548340663332467</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.488538008102863</v>
+        <v>1.34457745406916</v>
       </c>
       <c r="F1898" t="n">
         <v>-0.03253176124190804</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-3.924379339925412</v>
+        <v>-4.284280725009671</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.580901667270229</v>
+        <v>1.436941113236526</v>
       </c>
       <c r="F1899" t="n">
         <v>0.2315281770808881</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-3.217299716420575</v>
+        <v>-3.577201101504833</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.860946483011864</v>
+        <v>1.71698592897816</v>
       </c>
       <c r="F1900" t="n">
         <v>0.2315281770808881</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-2.967658686434623</v>
+        <v>-3.327560071518882</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.961146518894085</v>
+        <v>1.817185964860382</v>
       </c>
       <c r="F1901" t="n">
         <v>0.4811692070668399</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-2.713116787093548</v>
+        <v>-3.073018172177806</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.062330099851272</v>
+        <v>1.918369545817569</v>
       </c>
       <c r="F1902" t="n">
         <v>0.7357111064079154</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-2.479635564863949</v>
+        <v>-2.839536949948207</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.163647017580964</v>
+        <v>2.019686463547261</v>
       </c>
       <c r="F1903" t="n">
         <v>0.9691923286375139</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-2.299927034720076</v>
+        <v>-2.659828419804335</v>
       </c>
       <c r="E1904" t="n">
-        <v>2.232638219325554</v>
+        <v>2.088677665291851</v>
       </c>
       <c r="F1904" t="n">
         <v>1.02636383280021</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860424</v>
+        <v>3.763178672860426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-2.16765156108919</v>
+        <v>-2.527552946173448</v>
       </c>
       <c r="E1905" t="n">
-        <v>2.280915895524936</v>
+        <v>2.136955341491233</v>
       </c>
       <c r="F1905" t="n">
         <v>1.158639306431097</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575949</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-1.977051886416037</v>
+        <v>-2.336953271500295</v>
       </c>
       <c r="E1906" t="n">
-        <v>2.359970826081834</v>
+        <v>2.216010272048131</v>
       </c>
       <c r="F1906" t="n">
         <v>1.34923898110425</v>
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.415092192862865</v>
+        <v>3.398678966300933</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-1.761953401913797</v>
+        <v>-1.794773177502518</v>
       </c>
       <c r="E1907" t="n">
-        <v>2.458916561106388</v>
+        <v>2.4457886508709</v>
       </c>
       <c r="F1907" t="n">
-        <v>1.564337465606489</v>
+        <v>1.891419075102027</v>
       </c>
       <c r="G1907" t="n">
-        <v>4.102656825549548</v>
+        <v>4.298905791246871</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240319.xlsx
+++ b/tame_output/ON/bt/strategyON_20240319.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-60.8%</t>
+          <t>-62.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>102.3%</t>
+          <t>100.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1002,22 +1002,22 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-52.0%</t>
+          <t>-55.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-105.4%</t>
+          <t>-106.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-341.0%</t>
+          <t>-370.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-131.6%</t>
+          <t>-143.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-36.8%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-34.9%</t>
+          <t>-64.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>102.4%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.2%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-33.7%</t>
         </is>
       </c>
     </row>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880266</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860581</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628916</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-1.794773177502518</v>
+        <v>-2.087953472816715</v>
       </c>
       <c r="E1907" t="n">
-        <v>2.4457886508709</v>
+        <v>2.328516532745221</v>
       </c>
       <c r="F1907" t="n">
-        <v>1.891419075102027</v>
+        <v>1.59823877978783</v>
       </c>
       <c r="G1907" t="n">
-        <v>4.298905791246871</v>
+        <v>4.122997614058353</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240319.xlsx
+++ b/tame_output/ON/bt/strategyON_20240319.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-62.5%</t>
+          <t>-61.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>85.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-472.2%</t>
+          <t>-479.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-38.0%</t>
+          <t>-37.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-55.7%</t>
+          <t>-54.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>82.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.7%</t>
+          <t>501.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-373.4%</t>
+          <t>-352.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-189.3%</t>
+          <t>-192.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-147.4%</t>
+          <t>-138.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-252.1%</t>
+          <t>-259.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>232.5%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-125.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-82.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-151.6%</t>
+          <t>-156.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-43.2%</t>
+          <t>-47.2%</t>
         </is>
       </c>
     </row>
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.08948531413510424</v>
+        <v>-0.1623286724710379</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.083003008478177</v>
+        <v>3.053865665143804</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.561945777791274</v>
+        <v>1.489102419455341</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.056321025120731</v>
+        <v>4.012615010119171</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2411823611790393</v>
+        <v>-0.314025719514973</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.020251081165666</v>
+        <v>2.991113737831293</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.410248730747339</v>
+        <v>1.337405372411406</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.963229688399434</v>
+        <v>3.919523673397873</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4628042947371568</v>
+        <v>-0.5356476530730905</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.931468524341341</v>
+        <v>2.902331181006968</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.37272259705997</v>
+        <v>1.299879238724037</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.940580224785934</v>
+        <v>3.896874209784373</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.670808353090234</v>
+        <v>-0.7436517114261677</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.853159045554035</v>
+        <v>2.824021702219662</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.37272259705997</v>
+        <v>1.299879238724037</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.945472369339859</v>
+        <v>3.901766354338299</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.9412083157991193</v>
+        <v>-1.014051674135053</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.74008051680847</v>
+        <v>2.710943173474096</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.102322634351085</v>
+        <v>1.029479276015151</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.778313848052516</v>
+        <v>3.734607833050956</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-0.9478432382960496</v>
+        <v>-1.020686596631983</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.730510847116146</v>
+        <v>2.701373503781773</v>
       </c>
       <c r="F1851" t="n">
-        <v>1.095687711854155</v>
+        <v>1.022844353518221</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.767417193860807</v>
+        <v>3.723711178859246</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.275860460023529</v>
+        <v>-1.348703818359463</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.619642248163923</v>
+        <v>2.59050490482955</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.7676704901266754</v>
+        <v>0.6948271317907418</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.590945150563087</v>
+        <v>3.547239135561527</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.272523713514557</v>
+        <v>-1.345367071850491</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.62907569717608</v>
+        <v>2.599938353841707</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.7703625225457068</v>
+        <v>0.6975191642097732</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.600659120423075</v>
+        <v>3.556953105421515</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.639234765181103</v>
+        <v>-1.712078123517037</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.483497668553194</v>
+        <v>2.454360325218821</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.4036514708791612</v>
+        <v>0.3308081125432276</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.381738881466879</v>
+        <v>3.33803286646532</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-1.639665464229698</v>
+        <v>-1.712508822565632</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.481867927746619</v>
+        <v>2.452730584412246</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.4036514708791612</v>
+        <v>0.3308081125432276</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.380281420279743</v>
+        <v>3.336575405278183</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-1.983348237456361</v>
+        <v>-2.056191595792295</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.346163941910571</v>
+        <v>2.317026598576197</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.295745418851943</v>
+        <v>0.2229020605160094</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.317306912518028</v>
+        <v>3.273600897516468</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-2.340998587694709</v>
+        <v>-2.413841946030643</v>
       </c>
       <c r="E1857" t="n">
-        <v>2.199209860471489</v>
+        <v>2.170072517137116</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.06190493138640513</v>
+        <v>-0.1347482897223387</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.098822761031277</v>
+        <v>3.055116746029717</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-2.347659527916857</v>
+        <v>-2.420502886252791</v>
       </c>
       <c r="E1858" t="n">
-        <v>2.19831841108289</v>
+        <v>2.169181067748516</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.06190493138640513</v>
+        <v>-0.1347482897223387</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.100595687731537</v>
+        <v>3.056889672729977</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-2.779465321066644</v>
+        <v>-2.852308679402578</v>
       </c>
       <c r="E1859" t="n">
-        <v>2.011928981290379</v>
+        <v>1.982791637956005</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.1983224278276721</v>
+        <v>-0.2711657861636057</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.005078077334181</v>
+        <v>2.961372062332621</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.105897849934388</v>
+        <v>-3.178741208270322</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.869640744745372</v>
+        <v>1.840503401410998</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.2807906783348203</v>
+        <v>-0.3536340366707539</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.943881902031983</v>
+        <v>2.900175887030422</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.107462001044691</v>
+        <v>-3.180305359380625</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.867595675957216</v>
+        <v>1.838458332622842</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.2807906783348203</v>
+        <v>-0.3536340366707539</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.942462493687948</v>
+        <v>2.898756478686388</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-3.471088245945004</v>
+        <v>-3.543931604280938</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.728632738231332</v>
+        <v>1.699495394896959</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3790123152019461</v>
+        <v>-0.4518556735378797</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.890017071801914</v>
+        <v>2.846311056800354</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-3.468661181416286</v>
+        <v>-3.54150453975222</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.728858079048651</v>
+        <v>1.699720735714277</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.3793450970090977</v>
+        <v>-0.4521884553450313</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.889071917723454</v>
+        <v>2.845365902721894</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-3.877249958596964</v>
+        <v>-3.950093316932898</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.564184112191139</v>
+        <v>1.535046768856765</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.7879338741897761</v>
+        <v>-0.8607772325257097</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.642680195429806</v>
+        <v>2.598974180428246</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.290232442738057</v>
+        <v>-4.363075801073991</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.394176551006162</v>
+        <v>1.365039207671788</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.7879338741897761</v>
+        <v>-0.8607772325257097</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.637865627901267</v>
+        <v>2.594159612899707</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-4.706624317025055</v>
+        <v>-4.779467675360989</v>
       </c>
       <c r="E1866" t="n">
-        <v>1.22561385190024</v>
+        <v>1.196476508565866</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.7879338741897761</v>
+        <v>-0.8607772325257097</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.635859678510144</v>
+        <v>2.592153663508584</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.083301327554899</v>
+        <v>-5.156144685890833</v>
       </c>
       <c r="E1867" t="n">
-        <v>1.085201738356981</v>
+        <v>1.056064395022608</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.7879338741897761</v>
+        <v>-0.8607772325257097</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.646118369178823</v>
+        <v>2.602412354177263</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.097016191880011</v>
+        <v>-5.169859550215945</v>
       </c>
       <c r="E1868" t="n">
-        <v>1.075815357772632</v>
+        <v>1.046678014438259</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.7879338741897761</v>
+        <v>-0.8607772325257097</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.642217934324519</v>
+        <v>2.598511919322958</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-5.40984099112499</v>
+        <v>-5.482684349460924</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.949090358129641</v>
+        <v>0.9199530147952677</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.7879338741897761</v>
+        <v>-0.8607772325257097</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.64062285437952</v>
+        <v>2.596916839377959</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-5.414654029590327</v>
+        <v>-5.487497387926261</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.9509441186727146</v>
+        <v>0.9218067753383408</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.7894805088925619</v>
+        <v>-0.8623238672284955</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.643473849487056</v>
+        <v>2.599767834485496</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-5.848003137700563</v>
+        <v>-5.920846496036497</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.7735781708942171</v>
+        <v>0.7444408275598433</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.7894805088925619</v>
+        <v>-0.8623238672284955</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.639447544952653</v>
+        <v>2.595741529951093</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.231004526443194</v>
+        <v>-6.303847884779128</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.6202755140755802</v>
+        <v>0.5911381707412069</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.7894805088925619</v>
+        <v>-0.8623238672284955</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.639345443631069</v>
+        <v>2.595639428629509</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-6.605989852614472</v>
+        <v>-6.678833210950406</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.4728528995784997</v>
+        <v>0.443715556244126</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.164465835063839</v>
+        <v>-1.237309193399773</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.416925763899733</v>
+        <v>2.373219748898173</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-6.965520175118473</v>
+        <v>-7.038363533454407</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.3343910738749489</v>
+        <v>0.3052537305405756</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.164465835063839</v>
+        <v>-1.237309193399773</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.422276067197783</v>
+        <v>2.378570052196223</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.291920203783486</v>
+        <v>-7.36476356211942</v>
       </c>
       <c r="E1875" t="n">
-        <v>0.2117470823661214</v>
+        <v>0.1826097390317476</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.490865863728852</v>
+        <v>-1.563709222064786</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.234352069955952</v>
+        <v>2.190646054954392</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.285444056989927</v>
+        <v>-7.358287415325861</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.2173792917053139</v>
+        <v>0.1882419483709405</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.484389716935293</v>
+        <v>-1.557233075271226</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.241279508653857</v>
+        <v>2.197573493652297</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.281753132033515</v>
+        <v>-7.354596490369449</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.2188556616878787</v>
+        <v>0.1897183183535049</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.484389716935293</v>
+        <v>-1.557233075271226</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.241279508653857</v>
+        <v>2.197573493652297</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-7.274537779161699</v>
+        <v>-7.347381137497633</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.2272549999552473</v>
+        <v>0.198117656620874</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.414611481644911</v>
+        <v>-1.487454839980844</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.288659646946729</v>
+        <v>2.244953631945168</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-7.223509933079873</v>
+        <v>-7.296353291415807</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.2521486928724141</v>
+        <v>0.2230113495380404</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.33940214333781</v>
+        <v>-1.412245501673743</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.338267804415425</v>
+        <v>2.294561789413865</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-7.150040101412425</v>
+        <v>-7.222883459748359</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.2969083270328143</v>
+        <v>0.2677709836984405</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.265932311670361</v>
+        <v>-1.338775670006295</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.397721404909316</v>
+        <v>2.354015389907755</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-7.069667745948495</v>
+        <v>-7.142511104284429</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.3436124899659032</v>
+        <v>0.3144751466315294</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.185559956206432</v>
+        <v>-1.258403314542365</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.46050003893519</v>
+        <v>2.41679402393363</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-7.257940548314339</v>
+        <v>-7.330783906650273</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.2610842041179695</v>
+        <v>0.2319468607835957</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.185559956206432</v>
+        <v>-1.258403314542365</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.453280874033594</v>
+        <v>2.409574859032034</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-7.278105189863886</v>
+        <v>-7.35094854819982</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.2463461567241745</v>
+        <v>0.2172088133898007</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.205724597755979</v>
+        <v>-1.278567956091913</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.434509898329889</v>
+        <v>2.390803883328329</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-7.507929637027711</v>
+        <v>-7.580772995363645</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.1555321676972006</v>
+        <v>0.1263948243628272</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.36837213482614</v>
+        <v>-1.441215493162073</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.338037165926349</v>
+        <v>2.294331150924789</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-7.444860404721372</v>
+        <v>-7.517703763057306</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.1834535892488511</v>
+        <v>0.1543162459144773</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.396885697508374</v>
+        <v>-1.469729055844307</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.323622756946123</v>
+        <v>2.279916741944564</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-7.67123105460261</v>
+        <v>-7.465688249088494</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.09689566498275681</v>
+        <v>0.1791127871884033</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.396885697508374</v>
+        <v>-1.469729055844307</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.327613092632524</v>
+        <v>2.283907077630964</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-7.495661385681706</v>
+        <v>-7.29011858016759</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.1656483056523763</v>
+        <v>0.2478654278580228</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.396885697508374</v>
+        <v>-1.469729055844307</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.326137865733783</v>
+        <v>2.282431850732222</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-7.298391979953708</v>
+        <v>-7.092849174439592</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.2596094781084481</v>
+        <v>0.3418266003140946</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.199616291780376</v>
+        <v>-1.272459650116309</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.459552919335454</v>
+        <v>2.415846904333894</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-7.099239872716609</v>
+        <v>-6.893697067202493</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.3262191873566045</v>
+        <v>0.408436309562251</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.034293765830562</v>
+        <v>-1.107137124166496</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.545695301258659</v>
+        <v>2.501989286257099</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-6.873394719997198</v>
+        <v>-6.667851914483082</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.4261363214805778</v>
+        <v>0.5083534436862243</v>
       </c>
       <c r="F1890" t="n">
-        <v>-0.9923670902433988</v>
+        <v>-1.065210448579332</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.580430379647166</v>
+        <v>2.536724364645606</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-6.587119907674504</v>
+        <v>-6.381577102160388</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.5417853909657144</v>
+        <v>0.6240025131713609</v>
       </c>
       <c r="F1891" t="n">
-        <v>-0.9923670902433988</v>
+        <v>-1.065210448579332</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.581569524203225</v>
+        <v>2.537863509201665</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-6.36032408060117</v>
+        <v>-6.154781275087054</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.6351374959571556</v>
+        <v>0.7173546181628017</v>
       </c>
       <c r="F1892" t="n">
-        <v>-0.9242531456218542</v>
+        <v>-0.9970965039577878</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.625071665138259</v>
+        <v>2.581365650136699</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-6.076415349672421</v>
+        <v>-5.870872544158305</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.7544346925672918</v>
+        <v>0.8366518147729378</v>
       </c>
       <c r="F1893" t="n">
-        <v>-0.9242531456218542</v>
+        <v>-0.9970965039577878</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.630805369376895</v>
+        <v>2.587099354375336</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-5.829428099479468</v>
+        <v>-5.623885293965353</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.8434923302506077</v>
+        <v>0.9257094524562537</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.6772658954289021</v>
+        <v>-0.7501092537648357</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.769260457098802</v>
+        <v>2.725554442097241</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-5.565591232275399</v>
+        <v>-5.360048426761284</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.9391435958193277</v>
+        <v>1.021360718024974</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.6772658954289021</v>
+        <v>-0.7501092537648357</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.759376975785894</v>
+        <v>2.715670960784334</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-5.298349431407003</v>
+        <v>-5.092806625892887</v>
       </c>
       <c r="E1896" t="n">
-        <v>1.044205755667313</v>
+        <v>1.126422877872959</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.6772658954289021</v>
+        <v>-0.7501092537648357</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.75754241528652</v>
+        <v>2.71383640028496</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-5.022540268006519</v>
+        <v>-4.816997462492403</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.154229106054045</v>
+        <v>1.236446228259692</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.5882465871501686</v>
+        <v>-0.6610899454861022</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.810653685280299</v>
+        <v>2.766947670278739</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-4.753472680239539</v>
+        <v>-4.547929874725424</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.262524647306331</v>
+        <v>1.344741769511977</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.3191789993831893</v>
+        <v>-0.3920223577191229</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.972762744085981</v>
+        <v>2.92905672908442</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-4.489412741916743</v>
+        <v>-4.283869936402628</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.354888306473697</v>
+        <v>1.437105428679343</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.0551190610603931</v>
+        <v>-0.1279624193963267</v>
       </c>
       <c r="G1899" t="n">
-        <v>3.117938390917906</v>
+        <v>3.074232375916346</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-3.782333118411905</v>
+        <v>-3.57679031289779</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.634933122215331</v>
+        <v>1.717150244420977</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.0551190610603931</v>
+        <v>-0.1279624193963267</v>
       </c>
       <c r="G1900" t="n">
-        <v>3.115151357257605</v>
+        <v>3.071445342256045</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-3.532692088425954</v>
+        <v>-3.327149282911838</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.735133158097553</v>
+        <v>1.817350280303199</v>
       </c>
       <c r="F1901" t="n">
-        <v>0.1945219689255586</v>
+        <v>0.121678610589625</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.265279599137018</v>
+        <v>3.221573584135458</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-3.278150189084878</v>
+        <v>-3.072607383570763</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.83631673905474</v>
+        <v>1.918533861260387</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.4490638682666341</v>
+        <v>0.3762205099307006</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.41737155996242</v>
+        <v>3.37366554496086</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-3.04466896685528</v>
+        <v>-2.839126161341164</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.937633656784432</v>
+        <v>2.019850778990079</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.6825450904962327</v>
+        <v>0.6097017321602991</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.565384722138031</v>
+        <v>3.521678707136471</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-2.864960436711407</v>
+        <v>-2.659417631197292</v>
       </c>
       <c r="E1904" t="n">
-        <v>2.006624858529022</v>
+        <v>2.088841980734668</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.7397165946589288</v>
+        <v>0.6668732363229952</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.59679541432269</v>
+        <v>3.55308939932113</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-2.73268496308052</v>
+        <v>-2.527142157566405</v>
       </c>
       <c r="E1905" t="n">
-        <v>2.054902534728404</v>
+        <v>2.13711965693405</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.8719920682898155</v>
+        <v>0.7991487099538819</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.671528185248249</v>
+        <v>3.627822170246689</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-2.542085288407367</v>
+        <v>-2.336542482893252</v>
       </c>
       <c r="E1906" t="n">
-        <v>2.133957465285302</v>
+        <v>2.216174587490948</v>
       </c>
       <c r="F1906" t="n">
-        <v>1.062591742962968</v>
+        <v>0.9897483846270347</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.788703050739778</v>
+        <v>3.744997035738217</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-2.293085489723787</v>
+        <v>-2.087542684209672</v>
       </c>
       <c r="E1907" t="n">
-        <v>2.246463725982393</v>
+        <v>2.328680848188039</v>
       </c>
       <c r="F1907" t="n">
-        <v>1.311591541646549</v>
+        <v>1.238748183310615</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.951009271173585</v>
+        <v>3.907303256172024</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.13601445393366</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.118404586479583</v>
+        <v>-1.905938228673286</v>
       </c>
       <c r="E1908" t="n">
-        <v>2.288296195028079</v>
+        <v>2.373282738150598</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.486272444890753</v>
+        <v>1.420352638847001</v>
       </c>
       <c r="G1908" t="n">
-        <v>4.027777920868112</v>
+        <v>3.988226037241861</v>
       </c>
     </row>
   </sheetData>
